--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2908-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2908-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0242E5A4-8E92-4C2D-9ABE-518A09210557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B3796D9-EC76-4AA2-B426-43742DB171E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{EA58BB01-E196-415A-92EE-225CF25F39C6}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{17EA3C54-9021-424B-B1E8-C98DC320E3A4}"/>
   </bookViews>
   <sheets>
     <sheet name="2908-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1586,27 +1586,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C77004-E755-4FD1-A8E7-0C97C9395D94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD45B325-5200-48BC-B52B-76B71EA1BB9A}">
   <dimension ref="A1:X45"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1640,7 +1639,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1676,7 +1675,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1728,7 +1727,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1796,7 +1795,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1868,7 +1867,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1940,7 +1939,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -2012,7 +2011,7 @@
         <v>6.56</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2084,7 +2083,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2156,7 +2155,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2228,7 +2227,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2300,7 +2299,7 @@
         <v>6.47</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2372,7 +2371,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2444,7 +2443,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2516,7 +2515,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2588,7 +2587,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2660,7 +2659,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2732,7 +2731,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="41">
         <v>2011</v>
       </c>
@@ -2804,7 +2803,7 @@
         <v>5.95</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="43"/>
       <c r="B19" s="44"/>
       <c r="C19" s="18" t="s">
@@ -2832,7 +2831,7 @@
       <c r="W19" s="50"/>
       <c r="X19" s="46"/>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2010</v>
       </c>
@@ -2904,7 +2903,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2009</v>
       </c>
@@ -2976,7 +2975,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2008</v>
       </c>
@@ -3048,7 +3047,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <v>2007</v>
       </c>
@@ -3120,7 +3119,7 @@
         <v>8.15</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="51">
         <v>2006</v>
       </c>
@@ -3192,7 +3191,7 @@
         <v>5.94</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="53"/>
       <c r="B25" s="54"/>
       <c r="C25" s="20" t="s">
@@ -3220,7 +3219,7 @@
       <c r="W25" s="60"/>
       <c r="X25" s="56"/>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2005</v>
       </c>
@@ -3292,7 +3291,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2004</v>
       </c>
@@ -3364,7 +3363,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2003</v>
       </c>
@@ -3436,7 +3435,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2002</v>
       </c>
@@ -3508,7 +3507,7 @@
         <v>9.93</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>2001</v>
       </c>
@@ -3580,7 +3579,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2000</v>
       </c>
@@ -3652,7 +3651,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>1999</v>
       </c>
@@ -3724,7 +3723,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>1998</v>
       </c>
@@ -3796,7 +3795,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>1997</v>
       </c>
@@ -3868,7 +3867,7 @@
         <v>6.15</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>1996</v>
       </c>
@@ -3940,7 +3939,7 @@
         <v>5.65</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>1995</v>
       </c>
@@ -4012,7 +4011,7 @@
         <v>5.52</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>1994</v>
       </c>
@@ -4084,7 +4083,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="41">
         <v>1993</v>
       </c>
@@ -4156,7 +4155,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="43"/>
       <c r="B39" s="44"/>
       <c r="C39" s="18" t="s">
@@ -4184,7 +4183,7 @@
       <c r="W39" s="50"/>
       <c r="X39" s="46"/>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>1992</v>
       </c>
@@ -4256,7 +4255,7 @@
         <v>6.33</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>1991</v>
       </c>
@@ -4328,7 +4327,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>1990</v>
       </c>
@@ -4400,7 +4399,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="39">
         <v>1989</v>
       </c>
@@ -4472,7 +4471,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>1988</v>
       </c>
@@ -4544,7 +4543,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="39" t="s">
         <v>64</v>
       </c>
